--- a/Translation Tables/csl_localization_ru_ru.xlsx
+++ b/Translation Tables/csl_localization_ru_ru.xlsx
@@ -848,7 +848,7 @@
     </row>
     <row r="58" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A58" t="str">
-        <v xml:space="preserve">CSL-UI_Empty</v>
+        <v xml:space="preserve">CSL-UI_CustomTitle</v>
       </c>
       <c r="B58" t="str">
         <v xml:space="preserve"/>
@@ -856,7 +856,7 @@
     </row>
     <row r="59" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A59" t="str">
-        <v xml:space="preserve">CSL-UI_Execute</v>
+        <v xml:space="preserve">CSL-UI_Custom_CharacterIdentity</v>
       </c>
       <c r="B59" t="str">
         <v xml:space="preserve"/>
@@ -864,7 +864,7 @@
     </row>
     <row r="60" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A60" t="str">
-        <v xml:space="preserve">CSL-UI_List</v>
+        <v xml:space="preserve">CSL-UI_Custom_Error1</v>
       </c>
       <c r="B60" t="str">
         <v xml:space="preserve"/>
@@ -872,7 +872,7 @@
     </row>
     <row r="61" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A61" t="str">
-        <v xml:space="preserve">CSL-UI_ListUnslotted</v>
+        <v xml:space="preserve">CSL-UI_Custom_Error2</v>
       </c>
       <c r="B61" t="str">
         <v xml:space="preserve"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="62" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A62" t="str">
-        <v xml:space="preserve">CSL-UI_Player</v>
+        <v xml:space="preserve">CSL-UI_Custom_Error3</v>
       </c>
       <c r="B62" t="str">
         <v xml:space="preserve"/>
@@ -888,7 +888,7 @@
     </row>
     <row r="63" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A63" t="str">
-        <v xml:space="preserve">CSL-UI_Players</v>
+        <v xml:space="preserve">CSL-UI_Custom_Error4</v>
       </c>
       <c r="B63" t="str">
         <v xml:space="preserve"/>
@@ -896,7 +896,7 @@
     </row>
     <row r="64" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A64" t="str">
-        <v xml:space="preserve">CSL-UI_RespawnTitle</v>
+        <v xml:space="preserve">CSL-UI_Custom_Error5</v>
       </c>
       <c r="B64" t="str">
         <v xml:space="preserve"/>
@@ -904,7 +904,7 @@
     </row>
     <row r="65" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A65" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
+        <v xml:space="preserve">CSL-UI_Custom_Name</v>
       </c>
       <c r="B65" t="str">
         <v xml:space="preserve"/>
@@ -912,7 +912,7 @@
     </row>
     <row r="66" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A66" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
+        <v xml:space="preserve">CSL-UI_Custom_NamePlaceholder</v>
       </c>
       <c r="B66" t="str">
         <v xml:space="preserve"/>
@@ -920,7 +920,7 @@
     </row>
     <row r="67" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A67" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Game</v>
+        <v xml:space="preserve">CSL-UI_Custom_Save</v>
       </c>
       <c r="B67" t="str">
         <v xml:space="preserve"/>
@@ -928,7 +928,7 @@
     </row>
     <row r="68" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A68" t="str">
-        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
+        <v xml:space="preserve">CSL-UI_Empty</v>
       </c>
       <c r="B68" t="str">
         <v xml:space="preserve"/>
@@ -936,7 +936,7 @@
     </row>
     <row r="69" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A69" t="str">
-        <v xml:space="preserve">CSL-UI_Time</v>
+        <v xml:space="preserve">CSL-UI_Execute</v>
       </c>
       <c r="B69" t="str">
         <v xml:space="preserve"/>
@@ -944,9 +944,89 @@
     </row>
     <row r="70" x14ac:dyDescent="0.20000000000000001" spans="1:1">
       <c r="A70" t="str">
+        <v xml:space="preserve">CSL-UI_List</v>
+      </c>
+      <c r="B70" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="71" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A71" t="str">
+        <v xml:space="preserve">CSL-UI_ListUnslotted</v>
+      </c>
+      <c r="B71" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="72" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A72" t="str">
+        <v xml:space="preserve">CSL-UI_Player</v>
+      </c>
+      <c r="B72" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="73" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A73" t="str">
+        <v xml:space="preserve">CSL-UI_Players</v>
+      </c>
+      <c r="B73" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="74" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A74" t="str">
+        <v xml:space="preserve">CSL-UI_RespawnTitle</v>
+      </c>
+      <c r="B74" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="75" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A75" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Briefing</v>
+      </c>
+      <c r="B75" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="76" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A76" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Debriefing</v>
+      </c>
+      <c r="B76" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="77" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A77" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Game</v>
+      </c>
+      <c r="B77" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="78" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A78" t="str">
+        <v xml:space="preserve">CSL-UI_Stage_Slotting</v>
+      </c>
+      <c r="B78" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="79" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A79" t="str">
+        <v xml:space="preserve">CSL-UI_Time</v>
+      </c>
+      <c r="B79" t="str">
+        <v xml:space="preserve"/>
+      </c>
+    </row>
+    <row r="80" x14ac:dyDescent="0.20000000000000001" spans="1:1">
+      <c r="A80" t="str">
         <v xml:space="preserve">CSL-UI_Weather</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B80" t="str">
         <v xml:space="preserve"/>
       </c>
     </row>
